--- a/data/dividends_info_20260503.xlsx
+++ b/data/dividends_info_20260503.xlsx
@@ -10057,7 +10057,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -10118,14 +10118,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -10135,14 +10135,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -10152,14 +10152,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -10169,14 +10169,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10186,14 +10186,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10210,7 +10210,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10220,14 +10220,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -10237,14 +10237,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -10271,14 +10271,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10305,14 +10305,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10322,14 +10322,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10339,14 +10339,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10363,7 +10363,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10380,7 +10380,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10397,7 +10397,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10407,14 +10407,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10431,7 +10431,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10448,7 +10448,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10458,14 +10458,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10482,7 +10482,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10492,14 +10492,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10516,7 +10516,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10526,14 +10526,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10550,7 +10550,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10567,7 +10567,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10584,7 +10584,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10594,14 +10594,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10611,14 +10611,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10628,14 +10628,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10652,7 +10652,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10662,14 +10662,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10679,14 +10679,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10696,14 +10696,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10713,14 +10713,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10730,14 +10730,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10764,14 +10764,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10788,7 +10788,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10798,14 +10798,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10815,14 +10815,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10839,7 +10839,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10849,14 +10849,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10866,14 +10866,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10883,14 +10883,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10924,7 +10924,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10934,14 +10934,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10951,14 +10951,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10975,7 +10975,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10992,7 +10992,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11009,7 +11009,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11026,7 +11026,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11043,7 +11043,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11060,7 +11060,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11111,7 +11111,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11128,7 +11128,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11145,7 +11145,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11155,14 +11155,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11172,14 +11172,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11189,14 +11189,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11206,14 +11206,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11223,14 +11223,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11240,14 +11240,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11264,7 +11264,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11274,14 +11274,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11291,14 +11291,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11315,7 +11315,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11325,14 +11325,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11349,7 +11349,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11359,14 +11359,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11376,14 +11376,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11393,14 +11393,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11417,7 +11417,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11434,7 +11434,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11451,7 +11451,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11468,7 +11468,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11502,7 +11502,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11519,7 +11519,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11529,14 +11529,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11553,7 +11553,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11587,7 +11587,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11604,7 +11604,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11614,14 +11614,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11638,7 +11638,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11648,14 +11648,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11689,7 +11689,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11699,14 +11699,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11716,14 +11716,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11733,14 +11733,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11750,14 +11750,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11767,14 +11767,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11791,7 +11791,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11818,7 +11818,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -11835,14 +11835,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11859,7 +11859,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11876,7 +11876,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11886,14 +11886,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11903,14 +11903,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11927,7 +11927,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11944,7 +11944,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11961,7 +11961,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11971,14 +11971,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11995,7 +11995,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12012,7 +12012,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12029,7 +12029,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12039,14 +12039,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12063,7 +12063,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12080,7 +12080,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12090,14 +12090,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12114,7 +12114,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12124,14 +12124,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12141,14 +12141,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12175,14 +12175,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12192,14 +12192,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12209,14 +12209,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12233,7 +12233,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12250,7 +12250,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12260,14 +12260,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12277,14 +12277,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12294,14 +12294,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12318,7 +12318,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -12352,7 +12352,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12369,7 +12369,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12379,14 +12379,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12403,7 +12403,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12413,14 +12413,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12430,14 +12430,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12454,7 +12454,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12464,14 +12464,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12488,7 +12488,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12498,14 +12498,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12522,7 +12522,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12539,7 +12539,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12556,7 +12556,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12573,7 +12573,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12583,14 +12583,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12607,7 +12607,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12624,7 +12624,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12641,7 +12641,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12658,7 +12658,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12668,14 +12668,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12692,7 +12692,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12702,14 +12702,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12719,14 +12719,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12736,14 +12736,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12753,14 +12753,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12770,14 +12770,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12787,14 +12787,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12804,14 +12804,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12821,14 +12821,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12845,7 +12845,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12855,14 +12855,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12872,14 +12872,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12896,7 +12896,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12906,14 +12906,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12930,7 +12930,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12947,7 +12947,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12964,7 +12964,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12981,7 +12981,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12998,7 +12998,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -13015,7 +13015,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -13032,7 +13032,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -13042,14 +13042,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -13066,7 +13066,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -13083,7 +13083,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -13100,7 +13100,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -13110,14 +13110,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -13127,14 +13127,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -13168,7 +13168,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -13178,14 +13178,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13202,7 +13202,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13219,7 +13219,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13229,14 +13229,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13253,7 +13253,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13263,14 +13263,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13280,14 +13280,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13304,7 +13304,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -13314,14 +13314,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13338,7 +13338,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13355,7 +13355,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13365,14 +13365,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13389,7 +13389,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -13399,14 +13399,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -13416,14 +13416,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -13433,14 +13433,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -13450,14 +13450,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -13474,7 +13474,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -13508,7 +13508,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13518,14 +13518,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -13535,14 +13535,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -13559,7 +13559,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -13569,14 +13569,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13586,14 +13586,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -13603,14 +13603,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>DIADEMA CAPITAL</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -13620,14 +13620,14 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>DIADEMA CAPITAL</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -13637,7 +13637,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -13712,7 +13712,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13722,14 +13722,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13739,14 +13739,14 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13756,14 +13756,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13780,7 +13780,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13814,7 +13814,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13824,14 +13824,14 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13848,7 +13848,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13858,14 +13858,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -13933,7 +13933,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13943,14 +13943,14 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13960,14 +13960,14 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13977,14 +13977,14 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -13994,14 +13994,14 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -14018,7 +14018,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -14052,7 +14052,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -14062,14 +14062,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -14079,14 +14079,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -14137,7 +14137,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -14154,7 +14154,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -14171,7 +14171,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>TALEA GROUP</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -14188,7 +14188,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>TALEA GROUP</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -14239,7 +14239,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -14266,14 +14266,14 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -14283,14 +14283,14 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -14307,7 +14307,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -14324,7 +14324,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -14341,7 +14341,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14351,14 +14351,14 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -14375,7 +14375,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -14426,7 +14426,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -14460,7 +14460,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14477,7 +14477,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14487,14 +14487,14 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14504,14 +14504,14 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14521,14 +14521,14 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14538,14 +14538,14 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14555,14 +14555,14 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14579,7 +14579,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14596,7 +14596,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14606,14 +14606,14 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14623,14 +14623,14 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -14640,14 +14640,14 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -14657,14 +14657,14 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -14674,14 +14674,14 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -14698,7 +14698,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -14708,14 +14708,14 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -14732,7 +14732,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -14742,14 +14742,14 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -14766,7 +14766,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -14783,7 +14783,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -14872,44 +14872,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>